--- a/multiSchoolOutput/04_School_of_Geosciences/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/04_School_of_Geosciences/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0228_-1_LG.08</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5675,7 +5675,7 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10719,12 +10719,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10841,12 +10841,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12244,12 +12244,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12305,12 +12305,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12427,12 +12427,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">

--- a/multiSchoolOutput/04_School_of_Geosciences/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/04_School_of_Geosciences/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -811,7 +811,7 @@
         <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -853,12 +853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1047,7 +1047,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1106,7 +1106,7 @@
         <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1527,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1588,7 +1588,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2076,7 +2076,7 @@
         <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2503,7 +2503,7 @@
         <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0226_01_1.07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2564,7 +2564,7 @@
         <v>45</v>
       </c>
       <c r="F36" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2625,7 +2625,7 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0335_00_G.13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2686,7 +2686,7 @@
         <v>45</v>
       </c>
       <c r="F38" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2808,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2930,7 +2930,7 @@
         <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3052,7 +3052,7 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0113_01M_01M.473</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3174,7 +3174,7 @@
         <v>45</v>
       </c>
       <c r="F46" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3235,7 +3235,7 @@
         <v>35</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3418,7 +3418,7 @@
         <v>11</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3479,7 +3479,7 @@
         <v>11</v>
       </c>
       <c r="F51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3523,12 +3523,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3540,7 +3540,7 @@
         <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3723,7 +3723,7 @@
         <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3767,12 +3767,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0227_00_G.02</t>
+          <t>0228_-1_LG.08</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3845,7 +3845,7 @@
         <v>25</v>
       </c>
       <c r="F57" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3906,7 +3906,7 @@
         <v>7</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3967,7 +3967,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4089,7 +4089,7 @@
         <v>7</v>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4133,12 +4133,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4150,7 +4150,7 @@
         <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4211,7 +4211,7 @@
         <v>8</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0003_03_3.02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4333,7 +4333,7 @@
         <v>45</v>
       </c>
       <c r="F65" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0214_01_1.10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4394,7 +4394,7 @@
         <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4438,12 +4438,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4455,7 +4455,7 @@
         <v>8</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4577,7 +4577,7 @@
         <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4621,12 +4621,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4638,7 +4638,7 @@
         <v>7</v>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4682,12 +4682,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4760,7 +4760,7 @@
         <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4821,7 +4821,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4865,12 +4865,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0228_-1_LG.08</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5126,7 +5126,7 @@
         <v>30</v>
       </c>
       <c r="F78" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5370,7 +5370,7 @@
         <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5475,12 +5475,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5492,7 +5492,7 @@
         <v>11</v>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5536,12 +5536,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5553,7 +5553,7 @@
         <v>30</v>
       </c>
       <c r="F85" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5675,7 +5675,7 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0450_01_1.55</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5797,7 +5797,7 @@
         <v>45</v>
       </c>
       <c r="F89" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5919,7 +5919,7 @@
         <v>8</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6041,7 +6041,7 @@
         <v>10</v>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0208_-1_B.1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6224,7 +6224,7 @@
         <v>45</v>
       </c>
       <c r="F96" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_11_11.06</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6590,7 +6590,7 @@
         <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6773,7 +6773,7 @@
         <v>11</v>
       </c>
       <c r="F105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6817,12 +6817,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6895,7 +6895,7 @@
         <v>90</v>
       </c>
       <c r="F107" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6939,12 +6939,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6956,7 +6956,7 @@
         <v>25</v>
       </c>
       <c r="F108" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7017,7 +7017,7 @@
         <v>11</v>
       </c>
       <c r="F109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -7061,12 +7061,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7078,7 +7078,7 @@
         <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7200,7 +7200,7 @@
         <v>11</v>
       </c>
       <c r="F112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7383,7 +7383,7 @@
         <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7444,7 +7444,7 @@
         <v>15</v>
       </c>
       <c r="F116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7505,7 +7505,7 @@
         <v>8</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7749,7 +7749,7 @@
         <v>7</v>
       </c>
       <c r="F121" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0283_01_1.20</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7810,7 +7810,7 @@
         <v>45</v>
       </c>
       <c r="F122" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7854,12 +7854,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7871,7 +7871,7 @@
         <v>11</v>
       </c>
       <c r="F123" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7932,7 +7932,7 @@
         <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7976,12 +7976,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8054,7 +8054,7 @@
         <v>35</v>
       </c>
       <c r="F126" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8237,7 +8237,7 @@
         <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8281,12 +8281,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8298,7 +8298,7 @@
         <v>11</v>
       </c>
       <c r="F130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8420,7 +8420,7 @@
         <v>15</v>
       </c>
       <c r="F132" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -8464,12 +8464,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_01M_01M.473</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8542,7 +8542,7 @@
         <v>45</v>
       </c>
       <c r="F134" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8664,7 +8664,7 @@
         <v>11</v>
       </c>
       <c r="F136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -8708,12 +8708,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8786,7 +8786,7 @@
         <v>11</v>
       </c>
       <c r="F138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -8830,12 +8830,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8908,7 +8908,7 @@
         <v>20</v>
       </c>
       <c r="F140" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0226_01_1.07</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8969,7 +8969,7 @@
         <v>45</v>
       </c>
       <c r="F141" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0226_-1_LG.18</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -9072,12 +9072,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9089,7 +9089,7 @@
         <v>15</v>
       </c>
       <c r="F143" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9150,7 +9150,7 @@
         <v>11</v>
       </c>
       <c r="F144" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0227_03_3.03</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9211,7 +9211,7 @@
         <v>15</v>
       </c>
       <c r="F145" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9455,7 +9455,7 @@
         <v>11</v>
       </c>
       <c r="F149" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0003_03_3.02</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>45</v>
       </c>
       <c r="F150" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0003_03_3.02</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9760,7 +9760,7 @@
         <v>45</v>
       </c>
       <c r="F154" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -9804,12 +9804,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9943,7 +9943,7 @@
         <v>15</v>
       </c>
       <c r="F157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10065,7 +10065,7 @@
         <v>11</v>
       </c>
       <c r="F159" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10126,7 +10126,7 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10248,7 +10248,7 @@
         <v>11</v>
       </c>
       <c r="F162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10309,7 +10309,7 @@
         <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0226_01_1.07</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10553,7 +10553,7 @@
         <v>45</v>
       </c>
       <c r="F167" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -10597,12 +10597,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10675,7 +10675,7 @@
         <v>30</v>
       </c>
       <c r="F169" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -10719,12 +10719,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10797,7 +10797,7 @@
         <v>120</v>
       </c>
       <c r="F171" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -10841,12 +10841,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0208_-1_B.1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10919,7 +10919,7 @@
         <v>45</v>
       </c>
       <c r="F173" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11224,7 +11224,7 @@
         <v>11</v>
       </c>
       <c r="F178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11451,12 +11451,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0283_01_1.20</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11468,7 +11468,7 @@
         <v>45</v>
       </c>
       <c r="F182" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -11512,12 +11512,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11634,12 +11634,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11651,7 +11651,7 @@
         <v>7</v>
       </c>
       <c r="F185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11712,7 +11712,7 @@
         <v>30</v>
       </c>
       <c r="F186" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -11756,12 +11756,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12017,7 +12017,7 @@
         <v>30</v>
       </c>
       <c r="F191" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -12061,12 +12061,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12078,7 +12078,7 @@
         <v>12</v>
       </c>
       <c r="F192" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -12122,12 +12122,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12139,7 +12139,7 @@
         <v>30</v>
       </c>
       <c r="F193" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -12183,12 +12183,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12200,7 +12200,7 @@
         <v>12</v>
       </c>
       <c r="F194" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -12244,12 +12244,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_02_2.03</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12261,7 +12261,7 @@
         <v>15</v>
       </c>
       <c r="F195" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -12305,12 +12305,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0227_02_2.39</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12322,7 +12322,7 @@
         <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -12366,12 +12366,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12427,12 +12427,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12444,7 +12444,7 @@
         <v>10</v>
       </c>
       <c r="F198" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -12488,12 +12488,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0335_00_G.13</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12505,7 +12505,7 @@
         <v>45</v>
       </c>
       <c r="F199" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12610,12 +12610,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0450_01_1.55</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12627,7 +12627,7 @@
         <v>45</v>
       </c>
       <c r="F201" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
